--- a/data/nzd0186/nzd0186.xlsx
+++ b/data/nzd0186/nzd0186.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J553"/>
+  <dimension ref="A1:J551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20250,106 +20250,34 @@
     <row r="551">
       <c r="A551" s="1" t="inlineStr">
         <is>
-          <t>2025-11-07 22:00:13+00:00</t>
+          <t>2025-11-30 22:06:00+00:00</t>
         </is>
       </c>
       <c r="B551" t="n">
-        <v>312.95</v>
+        <v>311.54</v>
       </c>
       <c r="C551" t="n">
-        <v>327.25</v>
+        <v>309.33</v>
       </c>
       <c r="D551" t="n">
-        <v>321.31</v>
+        <v>313.24</v>
       </c>
       <c r="E551" t="n">
-        <v>325.01</v>
+        <v>323.75</v>
       </c>
       <c r="F551" t="n">
-        <v>328.48</v>
+        <v>326.61</v>
       </c>
       <c r="G551" t="n">
-        <v>349.2</v>
+        <v>328.78</v>
       </c>
       <c r="H551" t="n">
-        <v>354.34</v>
+        <v>338.26</v>
       </c>
       <c r="I551" t="n">
-        <v>356.5</v>
+        <v>338.64</v>
       </c>
       <c r="J551" t="inlineStr">
-        <is>
-          <t>L9</t>
-        </is>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-14 22:06:00+00:00</t>
-        </is>
-      </c>
-      <c r="B552" t="n">
-        <v>323.13</v>
-      </c>
-      <c r="C552" t="n">
-        <v>328.24</v>
-      </c>
-      <c r="D552" t="n">
-        <v>321.43</v>
-      </c>
-      <c r="E552" t="n">
-        <v>325.35</v>
-      </c>
-      <c r="F552" t="n">
-        <v>328.35</v>
-      </c>
-      <c r="G552" t="n">
-        <v>366.39</v>
-      </c>
-      <c r="H552" t="n">
-        <v>355.64</v>
-      </c>
-      <c r="I552" t="n">
-        <v>376.8</v>
-      </c>
-      <c r="J552" t="inlineStr">
-        <is>
-          <t>L9</t>
-        </is>
-      </c>
-    </row>
-    <row r="553">
-      <c r="A553" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-23 22:00:11+00:00</t>
-        </is>
-      </c>
-      <c r="B553" t="n">
-        <v>323.13</v>
-      </c>
-      <c r="C553" t="n">
-        <v>328.24</v>
-      </c>
-      <c r="D553" t="n">
-        <v>321.43</v>
-      </c>
-      <c r="E553" t="n">
-        <v>325.35</v>
-      </c>
-      <c r="F553" t="n">
-        <v>328.35</v>
-      </c>
-      <c r="G553" t="n">
-        <v>366.39</v>
-      </c>
-      <c r="H553" t="n">
-        <v>355.64</v>
-      </c>
-      <c r="I553" t="n">
-        <v>393.75</v>
-      </c>
-      <c r="J553" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20366,7 +20294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B666"/>
+  <dimension ref="A1:B667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27029,6 +26957,16 @@
       </c>
       <c r="B666" t="n">
         <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>-0.41</v>
       </c>
     </row>
   </sheetData>
@@ -27197,28 +27135,28 @@
         <v>0.0593</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02664534950494983</v>
+        <v>0.02119059567578226</v>
       </c>
       <c r="J2" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="K2" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005404781036489892</v>
+        <v>0.0003396812070788346</v>
       </c>
       <c r="M2" t="n">
-        <v>6.998662862148096</v>
+        <v>7.002027741984493</v>
       </c>
       <c r="N2" t="n">
-        <v>69.09376151846379</v>
+        <v>69.21731739408345</v>
       </c>
       <c r="O2" t="n">
-        <v>8.312265727132633</v>
+        <v>8.319694549325922</v>
       </c>
       <c r="P2" t="n">
-        <v>316.0408275676258</v>
+        <v>316.0973012528195</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27275,28 +27213,28 @@
         <v>0.0791</v>
       </c>
       <c r="I3" t="n">
-        <v>0.259893065525227</v>
+        <v>0.2409559204537442</v>
       </c>
       <c r="J3" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="K3" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03946228711052435</v>
+        <v>0.03433177707632351</v>
       </c>
       <c r="M3" t="n">
-        <v>7.580586109319599</v>
+        <v>7.552108078655017</v>
       </c>
       <c r="N3" t="n">
-        <v>86.5227752117278</v>
+        <v>85.5370681171437</v>
       </c>
       <c r="O3" t="n">
-        <v>9.301761941252195</v>
+        <v>9.248625201463389</v>
       </c>
       <c r="P3" t="n">
-        <v>305.7346443369853</v>
+        <v>305.9304816172209</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27353,28 +27291,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1494665386495913</v>
+        <v>0.1450486520722808</v>
       </c>
       <c r="J4" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="K4" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01125494545100181</v>
+        <v>0.01051286085099123</v>
       </c>
       <c r="M4" t="n">
-        <v>8.36383934447929</v>
+        <v>8.399769307237433</v>
       </c>
       <c r="N4" t="n">
-        <v>103.2851233994407</v>
+        <v>103.7203879901678</v>
       </c>
       <c r="O4" t="n">
-        <v>10.16292887899156</v>
+        <v>10.18432069360386</v>
       </c>
       <c r="P4" t="n">
-        <v>315.8122693879587</v>
+        <v>315.8579958580867</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27431,28 +27369,28 @@
         <v>0.0631</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1031419216263622</v>
+        <v>0.1024198855243717</v>
       </c>
       <c r="J5" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="K5" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00760146611351431</v>
+        <v>0.007433870265922571</v>
       </c>
       <c r="M5" t="n">
-        <v>7.160327508183358</v>
+        <v>7.187879158649344</v>
       </c>
       <c r="N5" t="n">
-        <v>73.09170210178027</v>
+        <v>73.36020667430982</v>
       </c>
       <c r="O5" t="n">
-        <v>8.5493685206441</v>
+        <v>8.56505730712351</v>
       </c>
       <c r="P5" t="n">
-        <v>322.3502449269476</v>
+        <v>322.3577209828335</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27509,28 +27447,28 @@
         <v>0.0548</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09694913188977639</v>
+        <v>0.09723329140554604</v>
       </c>
       <c r="J6" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="K6" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01236110822924252</v>
+        <v>0.01232784239906182</v>
       </c>
       <c r="M6" t="n">
-        <v>5.030127470708403</v>
+        <v>5.046946287101505</v>
       </c>
       <c r="N6" t="n">
-        <v>39.52187245019763</v>
+        <v>39.67374633149939</v>
       </c>
       <c r="O6" t="n">
-        <v>6.286642382877973</v>
+        <v>6.298709894216386</v>
       </c>
       <c r="P6" t="n">
-        <v>327.1302425359125</v>
+        <v>327.1273249365901</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27587,28 +27525,28 @@
         <v>0.1959</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2528948610752722</v>
+        <v>0.2175495160049055</v>
       </c>
       <c r="J7" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="K7" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1171316407476395</v>
+        <v>0.1099410521175568</v>
       </c>
       <c r="M7" t="n">
-        <v>3.674454525314093</v>
+        <v>3.524862204366892</v>
       </c>
       <c r="N7" t="n">
-        <v>25.36942494207053</v>
+        <v>20.06885638057197</v>
       </c>
       <c r="O7" t="n">
-        <v>5.036807018545631</v>
+        <v>4.479827717733347</v>
       </c>
       <c r="P7" t="n">
-        <v>323.9340723763507</v>
+        <v>324.2996178632258</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27665,28 +27603,28 @@
         <v>0.0625</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02212747541700564</v>
+        <v>0.004076645781095268</v>
       </c>
       <c r="J8" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="K8" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00149397600985679</v>
+        <v>5.430501573988611e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.954079756030411</v>
+        <v>2.884659859741853</v>
       </c>
       <c r="N8" t="n">
-        <v>17.22184546658323</v>
+        <v>16.02839092453466</v>
       </c>
       <c r="O8" t="n">
-        <v>4.149921139802927</v>
+        <v>4.003547292656184</v>
       </c>
       <c r="P8" t="n">
-        <v>339.5731578020057</v>
+        <v>339.7598225352111</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27743,28 +27681,28 @@
         <v>0.0762</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07531281838446838</v>
+        <v>0.03575409318103824</v>
       </c>
       <c r="J9" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="K9" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008984791083813337</v>
+        <v>0.002593560285036545</v>
       </c>
       <c r="M9" t="n">
-        <v>4.125486960217772</v>
+        <v>3.931354126546107</v>
       </c>
       <c r="N9" t="n">
-        <v>32.92448763071794</v>
+        <v>25.74985906113429</v>
       </c>
       <c r="O9" t="n">
-        <v>5.737986374218567</v>
+        <v>5.074431895408026</v>
       </c>
       <c r="P9" t="n">
-        <v>340.7078771234191</v>
+        <v>341.1170794284238</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27802,7 +27740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J553"/>
+  <dimension ref="A1:J551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56408,154 +56346,50 @@
     <row r="551">
       <c r="A551" s="1" t="inlineStr">
         <is>
-          <t>2025-11-07 22:00:13+00:00</t>
+          <t>2025-11-30 22:06:00+00:00</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>-36.96171038553819,175.8431036168556</t>
+          <t>-36.96171292574643,175.8430881101274</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>-36.96239052813372,175.84342363738006</t>
+          <t>-36.96242281253832,175.84322655728195</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>-36.96312057687735,175.8435244746807</t>
+          <t>-36.96313791878756,175.84343650711745</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>-36.96383145469357,175.8438054713112</t>
+          <t>-36.96383509379045,175.8437920748478</t>
         </is>
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>-36.96451260602966,175.84416116502808</t>
+          <t>-36.96451913666126,175.84414181640545</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>-36.965100227945214,175.8447295453037</t>
+          <t>-36.9651720376957,175.84451852223566</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>-36.96575398232318,175.84509854118576</t>
+          <t>-36.96581059970426,175.8449324038455</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t>-36.96640614051406,175.84547563197694</t>
+          <t>-36.966472455556676,175.84529297684102</t>
         </is>
       </c>
       <c r="J551" t="inlineStr">
-        <is>
-          <t>L9</t>
-        </is>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-14 22:06:00+00:00</t>
-        </is>
-      </c>
-      <c r="B552" t="inlineStr">
-        <is>
-          <t>-36.961692045536054,175.84321557319885</t>
-        </is>
-      </c>
-      <c r="C552" t="inlineStr">
-        <is>
-          <t>-36.962388744555156,175.84343452517018</t>
-        </is>
-      </c>
-      <c r="D552" t="inlineStr">
-        <is>
-          <t>-36.9631203190046,175.8435257827482</t>
-        </is>
-      </c>
-      <c r="E552" t="inlineStr">
-        <is>
-          <t>-36.96383047271479,175.84380908622967</t>
-        </is>
-      </c>
-      <c r="F552" t="inlineStr">
-        <is>
-          <t>-36.964513060030875,175.8441598199368</t>
-        </is>
-      </c>
-      <c r="G552" t="inlineStr">
-        <is>
-          <t>-36.96503977665711,175.84490718878718</t>
-        </is>
-      </c>
-      <c r="H552" t="inlineStr">
-        <is>
-          <t>-36.965749405037606,175.84511197267582</t>
-        </is>
-      </c>
-      <c r="I552" t="inlineStr">
-        <is>
-          <t>-36.966330765307426,175.84568324071472</t>
-        </is>
-      </c>
-      <c r="J552" t="inlineStr">
-        <is>
-          <t>L9</t>
-        </is>
-      </c>
-    </row>
-    <row r="553">
-      <c r="A553" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-23 22:00:11+00:00</t>
-        </is>
-      </c>
-      <c r="B553" t="inlineStr">
-        <is>
-          <t>-36.961692045536054,175.84321557319885</t>
-        </is>
-      </c>
-      <c r="C553" t="inlineStr">
-        <is>
-          <t>-36.962388744555156,175.84343452517018</t>
-        </is>
-      </c>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>-36.9631203190046,175.8435257827482</t>
-        </is>
-      </c>
-      <c r="E553" t="inlineStr">
-        <is>
-          <t>-36.96383047271479,175.84380908622967</t>
-        </is>
-      </c>
-      <c r="F553" t="inlineStr">
-        <is>
-          <t>-36.964513060030875,175.8441598199368</t>
-        </is>
-      </c>
-      <c r="G553" t="inlineStr">
-        <is>
-          <t>-36.96503977665711,175.84490718878718</t>
-        </is>
-      </c>
-      <c r="H553" t="inlineStr">
-        <is>
-          <t>-36.965749405037606,175.84511197267582</t>
-        </is>
-      </c>
-      <c r="I553" t="inlineStr">
-        <is>
-          <t>-36.96626782860057,175.84585658856855</t>
-        </is>
-      </c>
-      <c r="J553" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0186/nzd0186.xlsx
+++ b/data/nzd0186/nzd0186.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J551"/>
+  <dimension ref="A1:J554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20278,6 +20278,114 @@
         <v>338.64</v>
       </c>
       <c r="J551" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>312.11</v>
+      </c>
+      <c r="C552" t="n">
+        <v>308.41</v>
+      </c>
+      <c r="D552" t="n">
+        <v>313.55</v>
+      </c>
+      <c r="E552" t="n">
+        <v>323.9</v>
+      </c>
+      <c r="F552" t="n">
+        <v>327.79</v>
+      </c>
+      <c r="G552" t="n">
+        <v>328.16</v>
+      </c>
+      <c r="H552" t="n">
+        <v>338.79</v>
+      </c>
+      <c r="I552" t="n">
+        <v>339.73</v>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>312.58</v>
+      </c>
+      <c r="C553" t="n">
+        <v>308.42</v>
+      </c>
+      <c r="D553" t="n">
+        <v>311.8</v>
+      </c>
+      <c r="E553" t="n">
+        <v>323.42</v>
+      </c>
+      <c r="F553" t="n">
+        <v>326.62</v>
+      </c>
+      <c r="G553" t="n">
+        <v>328.26</v>
+      </c>
+      <c r="H553" t="n">
+        <v>338.57</v>
+      </c>
+      <c r="I553" t="n">
+        <v>340.64</v>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:16+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>315.63</v>
+      </c>
+      <c r="C554" t="n">
+        <v>308.33</v>
+      </c>
+      <c r="D554" t="n">
+        <v>312.81</v>
+      </c>
+      <c r="E554" t="n">
+        <v>323.94</v>
+      </c>
+      <c r="F554" t="n">
+        <v>327.7</v>
+      </c>
+      <c r="G554" t="n">
+        <v>325.34</v>
+      </c>
+      <c r="H554" t="n">
+        <v>338.81</v>
+      </c>
+      <c r="I554" t="n">
+        <v>340.79</v>
+      </c>
+      <c r="J554" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20294,7 +20402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B667"/>
+  <dimension ref="A1:B672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26967,6 +27075,56 @@
       </c>
       <c r="B667" t="n">
         <v>-0.41</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2025-12-01 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -27135,28 +27293,28 @@
         <v>0.0593</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02119059567578226</v>
+        <v>0.01753264451433195</v>
       </c>
       <c r="J2" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="K2" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003396812070788346</v>
+        <v>0.0002353079167286554</v>
       </c>
       <c r="M2" t="n">
-        <v>7.002027741984493</v>
+        <v>6.980310094287216</v>
       </c>
       <c r="N2" t="n">
-        <v>69.21731739408345</v>
+        <v>68.91007833152474</v>
       </c>
       <c r="O2" t="n">
-        <v>8.319694549325922</v>
+        <v>8.301209449925038</v>
       </c>
       <c r="P2" t="n">
-        <v>316.0973012528195</v>
+        <v>316.1352462506894</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27213,28 +27371,28 @@
         <v>0.0791</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2409559204537442</v>
+        <v>0.2365570846689588</v>
       </c>
       <c r="J3" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="K3" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03433177707632351</v>
+        <v>0.0335117798415675</v>
       </c>
       <c r="M3" t="n">
-        <v>7.552108078655017</v>
+        <v>7.536795813577878</v>
       </c>
       <c r="N3" t="n">
-        <v>85.5370681171437</v>
+        <v>85.15254300201421</v>
       </c>
       <c r="O3" t="n">
-        <v>9.248625201463389</v>
+        <v>9.227813554792609</v>
       </c>
       <c r="P3" t="n">
-        <v>305.9304816172209</v>
+        <v>305.9761286802644</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27291,28 +27449,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1450486520722808</v>
+        <v>0.1371467213361257</v>
       </c>
       <c r="J4" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="K4" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01051286085099123</v>
+        <v>0.009505123106844149</v>
       </c>
       <c r="M4" t="n">
-        <v>8.399769307237433</v>
+        <v>8.396233983785228</v>
       </c>
       <c r="N4" t="n">
-        <v>103.7203879901678</v>
+        <v>103.4170106005313</v>
       </c>
       <c r="O4" t="n">
-        <v>10.18432069360386</v>
+        <v>10.16941545028677</v>
       </c>
       <c r="P4" t="n">
-        <v>315.8579958580867</v>
+        <v>315.9399968308664</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27369,28 +27527,28 @@
         <v>0.0631</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1024198855243717</v>
+        <v>0.1009508336825836</v>
       </c>
       <c r="J5" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="K5" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007433870265922571</v>
+        <v>0.007314847554553472</v>
       </c>
       <c r="M5" t="n">
-        <v>7.187879158649344</v>
+        <v>7.156373575121568</v>
       </c>
       <c r="N5" t="n">
-        <v>73.36020667430982</v>
+        <v>72.97140345111602</v>
       </c>
       <c r="O5" t="n">
-        <v>8.56505730712351</v>
+        <v>8.542330094951613</v>
       </c>
       <c r="P5" t="n">
-        <v>322.3577209828335</v>
+        <v>322.3729651304982</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27447,28 +27605,28 @@
         <v>0.0548</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09723329140554604</v>
+        <v>0.09460784648729993</v>
       </c>
       <c r="J6" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="K6" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01232784239906182</v>
+        <v>0.01181812102369617</v>
       </c>
       <c r="M6" t="n">
-        <v>5.046946287101505</v>
+        <v>5.032848391272089</v>
       </c>
       <c r="N6" t="n">
-        <v>39.67374633149939</v>
+        <v>39.48838745949502</v>
       </c>
       <c r="O6" t="n">
-        <v>6.298709894216386</v>
+        <v>6.283978632959776</v>
       </c>
       <c r="P6" t="n">
-        <v>327.1273249365901</v>
+        <v>327.154569376563</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27525,28 +27683,28 @@
         <v>0.1959</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2175495160049055</v>
+        <v>0.2144121344657928</v>
       </c>
       <c r="J7" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="K7" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1099410521175568</v>
+        <v>0.1081135573439183</v>
       </c>
       <c r="M7" t="n">
-        <v>3.524862204366892</v>
+        <v>3.521181417789264</v>
       </c>
       <c r="N7" t="n">
-        <v>20.06885638057197</v>
+        <v>20.01035337396317</v>
       </c>
       <c r="O7" t="n">
-        <v>4.479827717733347</v>
+        <v>4.473293347631381</v>
       </c>
       <c r="P7" t="n">
-        <v>324.2996178632258</v>
+        <v>324.3321854483886</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27603,28 +27761,28 @@
         <v>0.0625</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004076645781095268</v>
+        <v>0.002774481115563372</v>
       </c>
       <c r="J8" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="K8" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L8" t="n">
-        <v>5.430501573988611e-05</v>
+        <v>2.546596095998055e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.884659859741853</v>
+        <v>2.875224102160906</v>
       </c>
       <c r="N8" t="n">
-        <v>16.02839092453466</v>
+        <v>15.94847089988883</v>
       </c>
       <c r="O8" t="n">
-        <v>4.003547292656184</v>
+        <v>3.993553668086712</v>
       </c>
       <c r="P8" t="n">
-        <v>339.7598225352111</v>
+        <v>339.7733349752718</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27681,28 +27839,28 @@
         <v>0.0762</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03575409318103824</v>
+        <v>0.03385477707348673</v>
       </c>
       <c r="J9" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="K9" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002593560285036545</v>
+        <v>0.002354283493582243</v>
       </c>
       <c r="M9" t="n">
-        <v>3.931354126546107</v>
+        <v>3.917755901672735</v>
       </c>
       <c r="N9" t="n">
-        <v>25.74985906113429</v>
+        <v>25.62619544904361</v>
       </c>
       <c r="O9" t="n">
-        <v>5.074431895408026</v>
+        <v>5.062232259492211</v>
       </c>
       <c r="P9" t="n">
-        <v>341.1170794284238</v>
+        <v>341.1367846616213</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27740,7 +27898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J551"/>
+  <dimension ref="A1:J554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56395,6 +56553,162 @@
         </is>
       </c>
     </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>-36.96171189885398,175.8430943788049</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>-36.96242446998794,175.84321643932543</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>-36.963137252618694,175.84343988629354</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>-36.96383466056471,175.84379366966496</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>-36.9645150157283,175.84415402569715</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>-36.96517421800572,175.84451211506448</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>-36.96580873358768,175.84493787976942</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>-36.966468408341726,175.84530412433645</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>-36.961711052117856,175.84309954771425</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>-36.962424451972204,175.8432165493032</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>-36.963141013248105,175.84342081029854</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>-36.96383604688701,175.84378856625003</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>-36.9645191017381,175.84414191987403</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>-36.96517386634284,175.84451314847922</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>-36.96580950820214,175.84493560674446</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>-36.966465029473426,175.8453134309601</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:16+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>-36.961705557335485,175.84313309063356</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>-36.96242461411398,175.8432155595031</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>-36.96313884282807,175.84343181987305</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>-36.96383454503785,175.84379409494952</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>-36.96451533003678,175.84415309448005</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>-36.96518413489546,175.8444829727649</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>-36.96580866316816,175.84493808640806</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>-36.966464472517046,175.84531496501887</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0186/nzd0186.xlsx
+++ b/data/nzd0186/nzd0186.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J554"/>
+  <dimension ref="A1:J555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20388,6 +20388,42 @@
       <c r="J554" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>315.81</v>
+      </c>
+      <c r="C555" t="n">
+        <v>308.08</v>
+      </c>
+      <c r="D555" t="n">
+        <v>313.55</v>
+      </c>
+      <c r="E555" t="n">
+        <v>324.18</v>
+      </c>
+      <c r="F555" t="n">
+        <v>328.05</v>
+      </c>
+      <c r="G555" t="n">
+        <v>325.4</v>
+      </c>
+      <c r="H555" t="n">
+        <v>339.46</v>
+      </c>
+      <c r="I555" t="n">
+        <v>341.2</v>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20402,7 +20438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B672"/>
+  <dimension ref="A1:B674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27125,6 +27161,26 @@
       </c>
       <c r="B672" t="n">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>0.18</v>
       </c>
     </row>
   </sheetData>
@@ -27293,28 +27349,28 @@
         <v>0.0593</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01753264451433195</v>
+        <v>0.01723495639961885</v>
       </c>
       <c r="J2" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K2" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002353079167286554</v>
+        <v>0.0002283483072391679</v>
       </c>
       <c r="M2" t="n">
-        <v>6.980310094287216</v>
+        <v>6.969022863032325</v>
       </c>
       <c r="N2" t="n">
-        <v>68.91007833152474</v>
+        <v>68.78679605338597</v>
       </c>
       <c r="O2" t="n">
-        <v>8.301209449925038</v>
+        <v>8.293780564578856</v>
       </c>
       <c r="P2" t="n">
-        <v>316.1352462506894</v>
+        <v>316.1383436102038</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27371,28 +27427,28 @@
         <v>0.0791</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2365570846689588</v>
+        <v>0.2349974786759468</v>
       </c>
       <c r="J3" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K3" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0335117798415675</v>
+        <v>0.03321026260469306</v>
       </c>
       <c r="M3" t="n">
-        <v>7.536795813577878</v>
+        <v>7.532233084907165</v>
       </c>
       <c r="N3" t="n">
-        <v>85.15254300201421</v>
+        <v>85.02914434583091</v>
       </c>
       <c r="O3" t="n">
-        <v>9.227813554792609</v>
+        <v>9.221124895902392</v>
       </c>
       <c r="P3" t="n">
-        <v>305.9761286802644</v>
+        <v>305.9923559336291</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27449,28 +27505,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1371467213361257</v>
+        <v>0.1348702923995506</v>
       </c>
       <c r="J4" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K4" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009505123106844149</v>
+        <v>0.009228032005630493</v>
       </c>
       <c r="M4" t="n">
-        <v>8.396233983785228</v>
+        <v>8.393098062582366</v>
       </c>
       <c r="N4" t="n">
-        <v>103.4170106005313</v>
+        <v>103.2949043918867</v>
       </c>
       <c r="O4" t="n">
-        <v>10.16941545028677</v>
+        <v>10.16341007693219</v>
       </c>
       <c r="P4" t="n">
-        <v>315.9399968308664</v>
+        <v>315.9636824215132</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27527,28 +27583,28 @@
         <v>0.0631</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1009508336825836</v>
+        <v>0.1006300638672512</v>
       </c>
       <c r="J5" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K5" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007314847554553472</v>
+        <v>0.007299276365495544</v>
       </c>
       <c r="M5" t="n">
-        <v>7.156373575121568</v>
+        <v>7.145092848309672</v>
       </c>
       <c r="N5" t="n">
-        <v>72.97140345111602</v>
+        <v>72.84096812232913</v>
       </c>
       <c r="O5" t="n">
-        <v>8.542330094951613</v>
+        <v>8.534692034416306</v>
       </c>
       <c r="P5" t="n">
-        <v>322.3729651304982</v>
+        <v>322.3763026484921</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27605,28 +27661,28 @@
         <v>0.0548</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09460784648729993</v>
+        <v>0.09400575965328019</v>
       </c>
       <c r="J6" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K6" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01181812102369617</v>
+        <v>0.01171755928245155</v>
       </c>
       <c r="M6" t="n">
-        <v>5.032848391272089</v>
+        <v>5.026793888115257</v>
       </c>
       <c r="N6" t="n">
-        <v>39.48838745949502</v>
+        <v>39.4216254825209</v>
       </c>
       <c r="O6" t="n">
-        <v>6.283978632959776</v>
+        <v>6.278664307201087</v>
       </c>
       <c r="P6" t="n">
-        <v>327.154569376563</v>
+        <v>327.1608339175093</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27683,28 +27739,28 @@
         <v>0.1959</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2144121344657928</v>
+        <v>0.2126781762901045</v>
       </c>
       <c r="J7" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K7" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1081135573439183</v>
+        <v>0.10678267728591</v>
       </c>
       <c r="M7" t="n">
-        <v>3.521181417789264</v>
+        <v>3.523422737928965</v>
       </c>
       <c r="N7" t="n">
-        <v>20.01035337396317</v>
+        <v>20.01169468239655</v>
       </c>
       <c r="O7" t="n">
-        <v>4.473293347631381</v>
+        <v>4.473443269160406</v>
       </c>
       <c r="P7" t="n">
-        <v>324.3321854483886</v>
+        <v>324.3502267862438</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27761,28 +27817,28 @@
         <v>0.0625</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002774481115563372</v>
+        <v>0.002629660866822424</v>
       </c>
       <c r="J8" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K8" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L8" t="n">
-        <v>2.546596095998055e-05</v>
+        <v>2.29736312244988e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.875224102160906</v>
+        <v>2.870720176600315</v>
       </c>
       <c r="N8" t="n">
-        <v>15.94847089988883</v>
+        <v>15.91994435965143</v>
       </c>
       <c r="O8" t="n">
-        <v>3.993553668086712</v>
+        <v>3.989980496149252</v>
       </c>
       <c r="P8" t="n">
-        <v>339.7733349752718</v>
+        <v>339.7748417884535</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27839,28 +27895,28 @@
         <v>0.0762</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03385477707348673</v>
+        <v>0.03354201433604063</v>
       </c>
       <c r="J9" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K9" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002354283493582243</v>
+        <v>0.002320762526217268</v>
       </c>
       <c r="M9" t="n">
-        <v>3.917755901672735</v>
+        <v>3.911945700914977</v>
       </c>
       <c r="N9" t="n">
-        <v>25.62619544904361</v>
+        <v>25.58115758030496</v>
       </c>
       <c r="O9" t="n">
-        <v>5.062232259492211</v>
+        <v>5.057781883425279</v>
       </c>
       <c r="P9" t="n">
-        <v>341.1367846616213</v>
+        <v>341.1400388682646</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27898,7 +27954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J554"/>
+  <dimension ref="A1:J555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56709,6 +56765,58 @@
         </is>
       </c>
     </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>-36.96170523305295,175.84313507021548</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>-36.96242506450772,175.8432128100583</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>-36.963137252618694,175.84343988629354</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>-36.9638338518766,175.8437966466569</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>-36.964514107725954,175.84415671587988</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>-36.9651839238979,175.8444835928139</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>-36.96580637453426,175.84494480216344</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>-36.966462950169515,175.8453191581127</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0186/nzd0186.xlsx
+++ b/data/nzd0186/nzd0186.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J555"/>
+  <dimension ref="A1:J556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20424,6 +20424,42 @@
       <c r="J555" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>318.04</v>
+      </c>
+      <c r="C556" t="n">
+        <v>307.61</v>
+      </c>
+      <c r="D556" t="n">
+        <v>314.91</v>
+      </c>
+      <c r="E556" t="n">
+        <v>322.31</v>
+      </c>
+      <c r="F556" t="n">
+        <v>327.49</v>
+      </c>
+      <c r="G556" t="n">
+        <v>324.62</v>
+      </c>
+      <c r="H556" t="n">
+        <v>340.17</v>
+      </c>
+      <c r="I556" t="n">
+        <v>341.53</v>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20438,7 +20474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B674"/>
+  <dimension ref="A1:B676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27181,6 +27217,26 @@
       </c>
       <c r="B674" t="n">
         <v>0.18</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-02-11 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>-0.26</v>
       </c>
     </row>
   </sheetData>
@@ -27349,28 +27405,28 @@
         <v>0.0593</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01723495639961885</v>
+        <v>0.01778481625425951</v>
       </c>
       <c r="J2" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K2" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002283483072391679</v>
+        <v>0.0002441700798700985</v>
       </c>
       <c r="M2" t="n">
-        <v>6.969022863032325</v>
+        <v>6.959251507836997</v>
       </c>
       <c r="N2" t="n">
-        <v>68.78679605338597</v>
+        <v>68.66661737571457</v>
       </c>
       <c r="O2" t="n">
-        <v>8.293780564578856</v>
+        <v>8.286532288944185</v>
       </c>
       <c r="P2" t="n">
-        <v>316.1383436102038</v>
+        <v>316.1326071103903</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27427,28 +27483,28 @@
         <v>0.0791</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2349974786759468</v>
+        <v>0.2332609088069453</v>
       </c>
       <c r="J3" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K3" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03321026260469306</v>
+        <v>0.03285813995181375</v>
       </c>
       <c r="M3" t="n">
-        <v>7.532233084907165</v>
+        <v>7.528671717389689</v>
       </c>
       <c r="N3" t="n">
-        <v>85.02914434583091</v>
+        <v>84.91345679719234</v>
       </c>
       <c r="O3" t="n">
-        <v>9.221124895902392</v>
+        <v>9.214849797863899</v>
       </c>
       <c r="P3" t="n">
-        <v>305.9923559336291</v>
+        <v>306.0104729731719</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27505,28 +27561,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1348702923995506</v>
+        <v>0.1331210722837103</v>
       </c>
       <c r="J4" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K4" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009228032005630493</v>
+        <v>0.00902702874030259</v>
       </c>
       <c r="M4" t="n">
-        <v>8.393098062582366</v>
+        <v>8.387141906251168</v>
       </c>
       <c r="N4" t="n">
-        <v>103.2949043918867</v>
+        <v>103.1468541650522</v>
       </c>
       <c r="O4" t="n">
-        <v>10.16341007693219</v>
+        <v>10.15612397349758</v>
       </c>
       <c r="P4" t="n">
-        <v>315.9636824215132</v>
+        <v>315.9819314367549</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27583,28 +27639,28 @@
         <v>0.0631</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1006300638672512</v>
+        <v>0.09959963241342565</v>
       </c>
       <c r="J5" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K5" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007299276365495544</v>
+        <v>0.007180583493531012</v>
       </c>
       <c r="M5" t="n">
-        <v>7.145092848309672</v>
+        <v>7.137438863027652</v>
       </c>
       <c r="N5" t="n">
-        <v>72.84096812232913</v>
+        <v>72.7229328885077</v>
       </c>
       <c r="O5" t="n">
-        <v>8.534692034416306</v>
+        <v>8.527774204826702</v>
       </c>
       <c r="P5" t="n">
-        <v>322.3763026484921</v>
+        <v>322.3870527874461</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27661,28 +27717,28 @@
         <v>0.0548</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09400575965328019</v>
+        <v>0.09319190683803645</v>
       </c>
       <c r="J6" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K6" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01171755928245155</v>
+        <v>0.01156400029247528</v>
       </c>
       <c r="M6" t="n">
-        <v>5.026793888115257</v>
+        <v>5.021802149973378</v>
       </c>
       <c r="N6" t="n">
-        <v>39.4216254825209</v>
+        <v>39.35883592585645</v>
       </c>
       <c r="O6" t="n">
-        <v>6.278664307201087</v>
+        <v>6.273662082536519</v>
       </c>
       <c r="P6" t="n">
-        <v>327.1608339175093</v>
+        <v>327.169324565596</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27739,28 +27795,28 @@
         <v>0.1959</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2126781762901045</v>
+        <v>0.2106558443923892</v>
       </c>
       <c r="J7" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K7" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L7" t="n">
-        <v>0.10678267728591</v>
+        <v>0.1051343814677471</v>
       </c>
       <c r="M7" t="n">
-        <v>3.523422737928965</v>
+        <v>3.527217164620502</v>
       </c>
       <c r="N7" t="n">
-        <v>20.01169468239655</v>
+        <v>20.02651924671525</v>
       </c>
       <c r="O7" t="n">
-        <v>4.473443269160406</v>
+        <v>4.475099914718692</v>
       </c>
       <c r="P7" t="n">
-        <v>324.3502267862438</v>
+        <v>324.3713250833026</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27817,28 +27873,28 @@
         <v>0.0625</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002629660866822424</v>
+        <v>0.002751721106072041</v>
       </c>
       <c r="J8" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K8" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L8" t="n">
-        <v>2.29736312244988e-05</v>
+        <v>2.526270520519791e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.870720176600315</v>
+        <v>2.866126051225679</v>
       </c>
       <c r="N8" t="n">
-        <v>15.91994435965143</v>
+        <v>15.89144513049147</v>
       </c>
       <c r="O8" t="n">
-        <v>3.989980496149252</v>
+        <v>3.986407546963992</v>
       </c>
       <c r="P8" t="n">
-        <v>339.7748417884535</v>
+        <v>339.7735683757216</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27895,28 +27951,28 @@
         <v>0.0762</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03354201433604063</v>
+        <v>0.03335499693046538</v>
       </c>
       <c r="J9" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K9" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002320762526217268</v>
+        <v>0.002304733610372867</v>
       </c>
       <c r="M9" t="n">
-        <v>3.911945700914977</v>
+        <v>3.905645154205823</v>
       </c>
       <c r="N9" t="n">
-        <v>25.58115758030496</v>
+        <v>25.53550053602556</v>
       </c>
       <c r="O9" t="n">
-        <v>5.057781883425279</v>
+        <v>5.053266323480839</v>
       </c>
       <c r="P9" t="n">
-        <v>341.1400388682646</v>
+        <v>341.1419899568978</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27954,7 +28010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J555"/>
+  <dimension ref="A1:J556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56817,6 +56873,58 @@
         </is>
       </c>
     </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>-36.96170121555006,175.84315959503476</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>-36.962425911247806,175.84320764110197</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>-36.96313433007034,175.84345471106536</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>-36.96383925275652,175.84377676460224</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>-36.96451606342323,175.84415092164008</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>-36.965186666866224,175.84447553217652</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>-36.965803874641445,175.84495213783418</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>-36.966461724865304,175.84532253304175</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0186/nzd0186.xlsx
+++ b/data/nzd0186/nzd0186.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J556"/>
+  <dimension ref="A1:J557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20460,6 +20460,42 @@
       <c r="J556" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>317.22</v>
+      </c>
+      <c r="C557" t="n">
+        <v>308.95</v>
+      </c>
+      <c r="D557" t="n">
+        <v>315.28</v>
+      </c>
+      <c r="E557" t="n">
+        <v>322.29</v>
+      </c>
+      <c r="F557" t="n">
+        <v>328.44</v>
+      </c>
+      <c r="G557" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="H557" t="n">
+        <v>340.01</v>
+      </c>
+      <c r="I557" t="n">
+        <v>342.39</v>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B676"/>
+  <dimension ref="A1:B678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27237,6 +27273,26 @@
       </c>
       <c r="B676" t="n">
         <v>-0.26</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-02-19 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>-0.41</v>
       </c>
     </row>
   </sheetData>
@@ -27405,28 +27461,28 @@
         <v>0.0593</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01778481625425951</v>
+        <v>0.01802063337837236</v>
       </c>
       <c r="J2" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K2" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002441700798700985</v>
+        <v>0.0002517562145604169</v>
       </c>
       <c r="M2" t="n">
-        <v>6.959251507836997</v>
+        <v>6.947920471119666</v>
       </c>
       <c r="N2" t="n">
-        <v>68.66661737571457</v>
+        <v>68.5438071323325</v>
       </c>
       <c r="O2" t="n">
-        <v>8.286532288944185</v>
+        <v>8.279118741287173</v>
       </c>
       <c r="P2" t="n">
-        <v>316.1326071103903</v>
+        <v>316.1301403586471</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27483,28 +27539,28 @@
         <v>0.0791</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2332609088069453</v>
+        <v>0.2320381718032304</v>
       </c>
       <c r="J3" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K3" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03285813995181375</v>
+        <v>0.03265342686349015</v>
       </c>
       <c r="M3" t="n">
-        <v>7.528671717389689</v>
+        <v>7.522130270680915</v>
       </c>
       <c r="N3" t="n">
-        <v>84.91345679719234</v>
+        <v>84.77930894268864</v>
       </c>
       <c r="O3" t="n">
-        <v>9.214849797863899</v>
+        <v>9.207568025417388</v>
       </c>
       <c r="P3" t="n">
-        <v>306.0104729731719</v>
+        <v>306.0232633447225</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27561,28 +27617,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1331210722837103</v>
+        <v>0.131522960498286</v>
       </c>
       <c r="J4" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K4" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00902702874030259</v>
+        <v>0.008848161088570006</v>
       </c>
       <c r="M4" t="n">
-        <v>8.387141906251168</v>
+        <v>8.380368818492078</v>
       </c>
       <c r="N4" t="n">
-        <v>103.1468541650522</v>
+        <v>102.9930673644121</v>
       </c>
       <c r="O4" t="n">
-        <v>10.15612397349758</v>
+        <v>10.14855001290392</v>
       </c>
       <c r="P4" t="n">
-        <v>315.9819314367549</v>
+        <v>315.9986483950645</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27639,28 +27695,28 @@
         <v>0.0631</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09959963241342565</v>
+        <v>0.0985637891632246</v>
       </c>
       <c r="J5" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K5" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007180583493531012</v>
+        <v>0.007061637559843237</v>
       </c>
       <c r="M5" t="n">
-        <v>7.137438863027652</v>
+        <v>7.129810994746856</v>
       </c>
       <c r="N5" t="n">
-        <v>72.7229328885077</v>
+        <v>72.60546629899972</v>
       </c>
       <c r="O5" t="n">
-        <v>8.527774204826702</v>
+        <v>8.520884126603278</v>
       </c>
       <c r="P5" t="n">
-        <v>322.3870527874461</v>
+        <v>322.3978881674157</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27717,28 +27773,28 @@
         <v>0.0548</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09319190683803645</v>
+        <v>0.09274174500836009</v>
       </c>
       <c r="J6" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K6" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01156400029247528</v>
+        <v>0.01150153827819611</v>
       </c>
       <c r="M6" t="n">
-        <v>5.021802149973378</v>
+        <v>5.015002287932688</v>
       </c>
       <c r="N6" t="n">
-        <v>39.35883592585645</v>
+        <v>39.29056422002848</v>
       </c>
       <c r="O6" t="n">
-        <v>6.273662082536519</v>
+        <v>6.268218584257292</v>
       </c>
       <c r="P6" t="n">
-        <v>327.169324565596</v>
+        <v>327.1740334580577</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27795,28 +27851,28 @@
         <v>0.1959</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2106558443923892</v>
+        <v>0.2082158953429754</v>
       </c>
       <c r="J7" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K7" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1051343814677471</v>
+        <v>0.1030155599052994</v>
       </c>
       <c r="M7" t="n">
-        <v>3.527217164620502</v>
+        <v>3.533221574824664</v>
       </c>
       <c r="N7" t="n">
-        <v>20.02651924671525</v>
+        <v>20.06446175563862</v>
       </c>
       <c r="O7" t="n">
-        <v>4.475099914718692</v>
+        <v>4.479337200483864</v>
       </c>
       <c r="P7" t="n">
-        <v>324.3713250833026</v>
+        <v>324.3968480328915</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27873,28 +27929,28 @@
         <v>0.0625</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002751721106072041</v>
+        <v>0.002815355683179279</v>
       </c>
       <c r="J8" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K8" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L8" t="n">
-        <v>2.526270520519791e-05</v>
+        <v>2.655765438597246e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.866126051225679</v>
+        <v>2.861270241810749</v>
       </c>
       <c r="N8" t="n">
-        <v>15.89144513049147</v>
+        <v>15.86291370183991</v>
       </c>
       <c r="O8" t="n">
-        <v>3.986407546963992</v>
+        <v>3.982827350242526</v>
       </c>
       <c r="P8" t="n">
-        <v>339.7735683757216</v>
+        <v>339.7729027298124</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27951,28 +28007,28 @@
         <v>0.0762</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03335499693046538</v>
+        <v>0.03349612327665577</v>
       </c>
       <c r="J9" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K9" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002304733610372867</v>
+        <v>0.00233413029529761</v>
       </c>
       <c r="M9" t="n">
-        <v>3.905645154205823</v>
+        <v>3.899391072050115</v>
       </c>
       <c r="N9" t="n">
-        <v>25.53550053602556</v>
+        <v>25.48982081112674</v>
       </c>
       <c r="O9" t="n">
-        <v>5.053266323480839</v>
+        <v>5.048744478692375</v>
       </c>
       <c r="P9" t="n">
-        <v>341.1419899568978</v>
+        <v>341.1405137127031</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28010,7 +28066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J556"/>
+  <dimension ref="A1:J557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56925,6 +56981,58 @@
         </is>
       </c>
     </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>-36.9617026928387,175.8431505769401</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>-36.96242349713719,175.84322237812606</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>-36.96313353496496,175.84345874427513</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>-36.96383931051993,175.84377655195993</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>-36.964512745722345,175.84416075115385</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>-36.96519060548649,175.84446395792685</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>-36.96580443799761,175.84495048472533</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>-36.966458531647824,175.84533132831086</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0186/nzd0186.xlsx
+++ b/data/nzd0186/nzd0186.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J557"/>
+  <dimension ref="A1:J560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20496,6 +20496,114 @@
       <c r="J557" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>316.39</v>
+      </c>
+      <c r="C558" t="n">
+        <v>309.57</v>
+      </c>
+      <c r="D558" t="n">
+        <v>315.66</v>
+      </c>
+      <c r="E558" t="n">
+        <v>322.63</v>
+      </c>
+      <c r="F558" t="n">
+        <v>328.13</v>
+      </c>
+      <c r="G558" t="n">
+        <v>324.39</v>
+      </c>
+      <c r="H558" t="n">
+        <v>340.32</v>
+      </c>
+      <c r="I558" t="n">
+        <v>342.42</v>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>317.49</v>
+      </c>
+      <c r="C559" t="n">
+        <v>310.5</v>
+      </c>
+      <c r="D559" t="n">
+        <v>316.45</v>
+      </c>
+      <c r="E559" t="n">
+        <v>323.74</v>
+      </c>
+      <c r="F559" t="n">
+        <v>328.62</v>
+      </c>
+      <c r="G559" t="n">
+        <v>325.54</v>
+      </c>
+      <c r="H559" t="n">
+        <v>340.8</v>
+      </c>
+      <c r="I559" t="n">
+        <v>342.66</v>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:59:37+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>317.49</v>
+      </c>
+      <c r="C560" t="n">
+        <v>310.5</v>
+      </c>
+      <c r="D560" t="n">
+        <v>316.45</v>
+      </c>
+      <c r="E560" t="n">
+        <v>323.23</v>
+      </c>
+      <c r="F560" t="n">
+        <v>328.33</v>
+      </c>
+      <c r="G560" t="n">
+        <v>325.72</v>
+      </c>
+      <c r="H560" t="n">
+        <v>340.44</v>
+      </c>
+      <c r="I560" t="n">
+        <v>342.25</v>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20510,7 +20618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B678"/>
+  <dimension ref="A1:B682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27293,6 +27401,46 @@
       </c>
       <c r="B678" t="n">
         <v>-0.41</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -27461,28 +27609,28 @@
         <v>0.0593</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01802063337837236</v>
+        <v>0.01859894806980703</v>
       </c>
       <c r="J2" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="K2" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002517562145604169</v>
+        <v>0.0002716142948246958</v>
       </c>
       <c r="M2" t="n">
-        <v>6.947920471119666</v>
+        <v>6.914316433548877</v>
       </c>
       <c r="N2" t="n">
-        <v>68.5438071323325</v>
+        <v>68.17877255745381</v>
       </c>
       <c r="O2" t="n">
-        <v>8.279118741287173</v>
+        <v>8.257043814674462</v>
       </c>
       <c r="P2" t="n">
-        <v>316.1301403586471</v>
+        <v>316.1240616292735</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27539,28 +27687,28 @@
         <v>0.0791</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2320381718032304</v>
+        <v>0.2298060304932334</v>
       </c>
       <c r="J3" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="K3" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03265342686349015</v>
+        <v>0.03243986880006966</v>
       </c>
       <c r="M3" t="n">
-        <v>7.522130270680915</v>
+        <v>7.49438873852096</v>
       </c>
       <c r="N3" t="n">
-        <v>84.77930894268864</v>
+        <v>84.34604666108183</v>
       </c>
       <c r="O3" t="n">
-        <v>9.207568025417388</v>
+        <v>9.184010380061743</v>
       </c>
       <c r="P3" t="n">
-        <v>306.0232633447225</v>
+        <v>306.0466889683369</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27617,28 +27765,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>0.131522960498286</v>
+        <v>0.1278074518531394</v>
       </c>
       <c r="J4" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="K4" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008848161088570006</v>
+        <v>0.008461506621042614</v>
       </c>
       <c r="M4" t="n">
-        <v>8.380368818492078</v>
+        <v>8.354471913985996</v>
       </c>
       <c r="N4" t="n">
-        <v>102.9930673644121</v>
+        <v>102.4984379214062</v>
       </c>
       <c r="O4" t="n">
-        <v>10.14855001290392</v>
+        <v>10.1241512198014</v>
       </c>
       <c r="P4" t="n">
-        <v>315.9986483950645</v>
+        <v>316.0376467718597</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27695,28 +27843,28 @@
         <v>0.0631</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0985637891632246</v>
+        <v>0.09652408155569984</v>
       </c>
       <c r="J5" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="K5" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007061637559843237</v>
+        <v>0.006859338537445248</v>
       </c>
       <c r="M5" t="n">
-        <v>7.129810994746856</v>
+        <v>7.10167865675957</v>
       </c>
       <c r="N5" t="n">
-        <v>72.60546629899972</v>
+        <v>72.23420467184023</v>
       </c>
       <c r="O5" t="n">
-        <v>8.520884126603278</v>
+        <v>8.499070812261786</v>
       </c>
       <c r="P5" t="n">
-        <v>322.3978881674157</v>
+        <v>322.4192960241318</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27773,28 +27921,28 @@
         <v>0.0548</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09274174500836009</v>
+        <v>0.09130992922423112</v>
       </c>
       <c r="J6" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="K6" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01150153827819611</v>
+        <v>0.01129271577893998</v>
       </c>
       <c r="M6" t="n">
-        <v>5.015002287932688</v>
+        <v>4.995109306254701</v>
       </c>
       <c r="N6" t="n">
-        <v>39.29056422002848</v>
+        <v>39.0884421607962</v>
       </c>
       <c r="O6" t="n">
-        <v>6.268218584257292</v>
+        <v>6.252075028404265</v>
       </c>
       <c r="P6" t="n">
-        <v>327.1740334580577</v>
+        <v>327.1890627152263</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27851,28 +27999,28 @@
         <v>0.1959</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2082158953429754</v>
+        <v>0.2029289611166683</v>
       </c>
       <c r="J7" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="K7" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1030155599052994</v>
+        <v>0.09897316915837817</v>
       </c>
       <c r="M7" t="n">
-        <v>3.533221574824664</v>
+        <v>3.54113590157131</v>
       </c>
       <c r="N7" t="n">
-        <v>20.06446175563862</v>
+        <v>20.07480451349082</v>
       </c>
       <c r="O7" t="n">
-        <v>4.479337200483864</v>
+        <v>4.480491548199909</v>
       </c>
       <c r="P7" t="n">
-        <v>324.3968480328915</v>
+        <v>324.4523387290899</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27929,28 +28077,28 @@
         <v>0.0625</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002815355683179279</v>
+        <v>0.003573663521102355</v>
       </c>
       <c r="J8" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="K8" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L8" t="n">
-        <v>2.655765438597246e-05</v>
+        <v>4.333450027593777e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.861270241810749</v>
+        <v>2.849429096140671</v>
       </c>
       <c r="N8" t="n">
-        <v>15.86291370183991</v>
+        <v>15.78038951458949</v>
       </c>
       <c r="O8" t="n">
-        <v>3.982827350242526</v>
+        <v>3.972453840460515</v>
       </c>
       <c r="P8" t="n">
-        <v>339.7729027298124</v>
+        <v>339.7649415562543</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28007,28 +28155,28 @@
         <v>0.0762</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03349612327665577</v>
+        <v>0.03396517731388601</v>
       </c>
       <c r="J9" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="K9" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00233413029529761</v>
+        <v>0.002430556997366273</v>
       </c>
       <c r="M9" t="n">
-        <v>3.899391072050115</v>
+        <v>3.880994381091794</v>
       </c>
       <c r="N9" t="n">
-        <v>25.48982081112674</v>
+        <v>25.35409504047032</v>
       </c>
       <c r="O9" t="n">
-        <v>5.048744478692375</v>
+        <v>5.035285000918053</v>
       </c>
       <c r="P9" t="n">
-        <v>341.1405137127031</v>
+        <v>341.1355910863857</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28066,7 +28214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J557"/>
+  <dimension ref="A1:J560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57033,6 +57181,162 @@
         </is>
       </c>
     </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>-36.96170418814237,175.8431414488683</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>-36.962422380160035,175.8432291967488</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>-36.963132718370105,175.84346288649047</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>-36.96383832854201,175.84378016687918</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>-36.964513828340614,175.8441575436284</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>-36.96518747569011,175.84447315532177</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>-36.96580334649501,175.8449536876237</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>-36.966458420256515,175.8453316351226</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>-36.96170220641446,175.84315354631278</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>-36.962420704693564,175.84323942468245</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>-36.963131020711934,175.8434714979378</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>-36.963835122672165,175.84379196852666</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>-36.96451211710524,175.84416261358794</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>-36.96518343157018,175.84448503959493</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>-36.9658016564263,175.84495864695006</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>-36.96645752912594,175.84533408961616</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:59:37+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>-36.96170220641446,175.84315354631278</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>-36.962420704693564,175.84323942468245</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>-36.963131020711934,175.8434714979378</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>-36.96383659563954,175.8437865461482</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>-36.964513129877226,175.84415961299968</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>-36.965182798577395,175.8444868997419</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>-36.96580292397785,175.84495492745532</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>-36.96645905147397,175.84532989652294</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0186/nzd0186.xlsx
+++ b/data/nzd0186/nzd0186.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J560"/>
+  <dimension ref="A1:J563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20604,6 +20604,114 @@
       <c r="J560" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 21:59:24+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>317.42</v>
+      </c>
+      <c r="C561" t="n">
+        <v>311.06</v>
+      </c>
+      <c r="D561" t="n">
+        <v>316.32</v>
+      </c>
+      <c r="E561" t="n">
+        <v>323.04</v>
+      </c>
+      <c r="F561" t="n">
+        <v>328.13</v>
+      </c>
+      <c r="G561" t="n">
+        <v>325.88</v>
+      </c>
+      <c r="H561" t="n">
+        <v>340.09</v>
+      </c>
+      <c r="I561" t="n">
+        <v>342.27</v>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 21:59:31+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>316.92</v>
+      </c>
+      <c r="C562" t="n">
+        <v>310.4</v>
+      </c>
+      <c r="D562" t="n">
+        <v>315.23</v>
+      </c>
+      <c r="E562" t="n">
+        <v>322.15</v>
+      </c>
+      <c r="F562" t="n">
+        <v>327.07</v>
+      </c>
+      <c r="G562" t="n">
+        <v>325.49</v>
+      </c>
+      <c r="H562" t="n">
+        <v>343.33</v>
+      </c>
+      <c r="I562" t="n">
+        <v>342.27</v>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>317.2</v>
+      </c>
+      <c r="C563" t="n">
+        <v>310.28</v>
+      </c>
+      <c r="D563" t="n">
+        <v>315.06</v>
+      </c>
+      <c r="E563" t="n">
+        <v>322.7</v>
+      </c>
+      <c r="F563" t="n">
+        <v>327.84</v>
+      </c>
+      <c r="G563" t="n">
+        <v>326.7</v>
+      </c>
+      <c r="H563" t="n">
+        <v>344.55</v>
+      </c>
+      <c r="I563" t="n">
+        <v>343.26</v>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20618,7 +20726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B682"/>
+  <dimension ref="A1:B685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27441,6 +27549,36 @@
       </c>
       <c r="B682" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
@@ -27609,28 +27747,28 @@
         <v>0.0593</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01859894806980703</v>
+        <v>0.01922238322513157</v>
       </c>
       <c r="J2" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="K2" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002716142948246958</v>
+        <v>0.0002938291907293999</v>
       </c>
       <c r="M2" t="n">
-        <v>6.914316433548877</v>
+        <v>6.880494411992411</v>
       </c>
       <c r="N2" t="n">
-        <v>68.17877255745381</v>
+        <v>67.81669063233062</v>
       </c>
       <c r="O2" t="n">
-        <v>8.257043814674462</v>
+        <v>8.235088987517416</v>
       </c>
       <c r="P2" t="n">
-        <v>316.1240616292735</v>
+        <v>316.1174926260277</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27687,28 +27825,28 @@
         <v>0.0791</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2298060304932334</v>
+        <v>0.2280422688663302</v>
       </c>
       <c r="J3" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="K3" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03243986880006966</v>
+        <v>0.03235057655849005</v>
       </c>
       <c r="M3" t="n">
-        <v>7.49438873852096</v>
+        <v>7.464293238400946</v>
       </c>
       <c r="N3" t="n">
-        <v>84.34604666108183</v>
+        <v>83.90955543385678</v>
       </c>
       <c r="O3" t="n">
-        <v>9.184010380061743</v>
+        <v>9.16021590541712</v>
       </c>
       <c r="P3" t="n">
-        <v>306.0466889683369</v>
+        <v>306.065278985795</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27765,28 +27903,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1278074518531394</v>
+        <v>0.1234533367133787</v>
       </c>
       <c r="J4" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="K4" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008461506621042614</v>
+        <v>0.007993283563314857</v>
       </c>
       <c r="M4" t="n">
-        <v>8.354471913985996</v>
+        <v>8.331940340207593</v>
       </c>
       <c r="N4" t="n">
-        <v>102.4984379214062</v>
+        <v>102.0327881553868</v>
       </c>
       <c r="O4" t="n">
-        <v>10.1241512198014</v>
+        <v>10.1011280635079</v>
       </c>
       <c r="P4" t="n">
-        <v>316.0376467718597</v>
+        <v>316.0835357437848</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27843,28 +27981,28 @@
         <v>0.0631</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09652408155569984</v>
+        <v>0.09389591919709762</v>
       </c>
       <c r="J5" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="K5" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006859338537445248</v>
+        <v>0.00657317941941693</v>
       </c>
       <c r="M5" t="n">
-        <v>7.10167865675957</v>
+        <v>7.076695242062038</v>
       </c>
       <c r="N5" t="n">
-        <v>72.23420467184023</v>
+        <v>71.87842070366885</v>
       </c>
       <c r="O5" t="n">
-        <v>8.499070812261786</v>
+        <v>8.478114218602439</v>
       </c>
       <c r="P5" t="n">
-        <v>322.4192960241318</v>
+        <v>322.4469922905753</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27921,28 +28059,28 @@
         <v>0.0548</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09130992922423112</v>
+        <v>0.08914949730775797</v>
       </c>
       <c r="J6" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="K6" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01129271577893998</v>
+        <v>0.01090101538693289</v>
       </c>
       <c r="M6" t="n">
-        <v>4.995109306254701</v>
+        <v>4.978986788815914</v>
       </c>
       <c r="N6" t="n">
-        <v>39.0884421607962</v>
+        <v>38.90051018387805</v>
       </c>
       <c r="O6" t="n">
-        <v>6.252075028404265</v>
+        <v>6.237027351541601</v>
       </c>
       <c r="P6" t="n">
-        <v>327.1890627152263</v>
+        <v>327.2118296397609</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27999,28 +28137,28 @@
         <v>0.1959</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2029289611166683</v>
+        <v>0.1986608040374826</v>
       </c>
       <c r="J7" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="K7" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09897316915837817</v>
+        <v>0.09600875672543852</v>
       </c>
       <c r="M7" t="n">
-        <v>3.54113590157131</v>
+        <v>3.543941536782417</v>
       </c>
       <c r="N7" t="n">
-        <v>20.07480451349082</v>
+        <v>20.04575656740815</v>
       </c>
       <c r="O7" t="n">
-        <v>4.480491548199909</v>
+        <v>4.477248772115321</v>
       </c>
       <c r="P7" t="n">
-        <v>324.4523387290899</v>
+        <v>324.4973111973408</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28077,28 +28215,28 @@
         <v>0.0625</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003573663521102355</v>
+        <v>0.006698833145474915</v>
       </c>
       <c r="J8" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="K8" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L8" t="n">
-        <v>4.333450027593777e-05</v>
+        <v>0.0001536130939308045</v>
       </c>
       <c r="M8" t="n">
-        <v>2.849429096140671</v>
+        <v>2.848572288689504</v>
       </c>
       <c r="N8" t="n">
-        <v>15.78038951458949</v>
+        <v>15.75607584595193</v>
       </c>
       <c r="O8" t="n">
-        <v>3.972453840460515</v>
+        <v>3.969392377424021</v>
       </c>
       <c r="P8" t="n">
-        <v>339.7649415562543</v>
+        <v>339.7319877732988</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28155,28 +28293,28 @@
         <v>0.0762</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03396517731388601</v>
+        <v>0.03459230714464305</v>
       </c>
       <c r="J9" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="K9" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002430556997366273</v>
+        <v>0.002552828149300024</v>
       </c>
       <c r="M9" t="n">
-        <v>3.880994381091794</v>
+        <v>3.863608786162824</v>
       </c>
       <c r="N9" t="n">
-        <v>25.35409504047032</v>
+        <v>25.22156763930496</v>
       </c>
       <c r="O9" t="n">
-        <v>5.035285000918053</v>
+        <v>5.022107888059053</v>
       </c>
       <c r="P9" t="n">
-        <v>341.1355910863857</v>
+        <v>341.1289770411464</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28214,7 +28352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J560"/>
+  <dimension ref="A1:J563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57337,6 +57475,162 @@
         </is>
       </c>
     </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 21:59:24+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>-36.96170233252446,175.84315277647542</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>-36.96241969581013,175.84324558343798</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>-36.96313130007344,175.84347008086425</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>-36.96383714439202,175.8437845260464</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>-36.964513828340614,175.8441575436284</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>-36.965182235917105,175.84448855320588</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>-36.96580415631952,175.84495131127974</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>-36.966458977213094,175.84533010106406</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 21:59:31+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>-36.96170323330998,175.84314727763712</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>-36.962420884851305,175.8432383249047</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>-36.96313364241164,175.84345819924678</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>-36.96383971486375,175.84377506346374</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>-36.96451753019602,175.84414657596002</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>-36.965183607401514,175.8444845228874</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>-36.96579274835256,175.8449847867289</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>-36.966458977213094,175.84533010106406</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>-36.961702728870115,175.8431503569866</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>-36.962421101040555,175.84323700517132</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>-36.96313400773034,175.84345634615042</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>-36.96383812637007,175.84378091112725</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>-36.964514841112475,175.84415454304</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>-36.96517935228283,175.84449702720823</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>-36.96578845275773,175.84499739167921</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>-36.96645530129929,175.84534022584978</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0186/nzd0186.xlsx
+++ b/data/nzd0186/nzd0186.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J563"/>
+  <dimension ref="A1:J567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20712,6 +20712,150 @@
       <c r="J563" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>318.84</v>
+      </c>
+      <c r="C564" t="n">
+        <v>312.02</v>
+      </c>
+      <c r="D564" t="n">
+        <v>316.7</v>
+      </c>
+      <c r="E564" t="n">
+        <v>323.75</v>
+      </c>
+      <c r="F564" t="n">
+        <v>328.03</v>
+      </c>
+      <c r="G564" t="n">
+        <v>328.23</v>
+      </c>
+      <c r="H564" t="n">
+        <v>346</v>
+      </c>
+      <c r="I564" t="n">
+        <v>342.99</v>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-11 21:58:57+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>318.84</v>
+      </c>
+      <c r="C565" t="n">
+        <v>312.02</v>
+      </c>
+      <c r="D565" t="n">
+        <v>316.7</v>
+      </c>
+      <c r="E565" t="n">
+        <v>325.19</v>
+      </c>
+      <c r="F565" t="n">
+        <v>328.03</v>
+      </c>
+      <c r="G565" t="n">
+        <v>328.23</v>
+      </c>
+      <c r="H565" t="n">
+        <v>346</v>
+      </c>
+      <c r="I565" t="n">
+        <v>339.36</v>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:15+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>318.94</v>
+      </c>
+      <c r="C566" t="n">
+        <v>310.63</v>
+      </c>
+      <c r="D566" t="n">
+        <v>318.77</v>
+      </c>
+      <c r="E566" t="n">
+        <v>326.09</v>
+      </c>
+      <c r="F566" t="n">
+        <v>329.93</v>
+      </c>
+      <c r="G566" t="n">
+        <v>329.17</v>
+      </c>
+      <c r="H566" t="n">
+        <v>347.24</v>
+      </c>
+      <c r="I566" t="n">
+        <v>339.58</v>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>316.44</v>
+      </c>
+      <c r="C567" t="n">
+        <v>310.22</v>
+      </c>
+      <c r="D567" t="n">
+        <v>316.86</v>
+      </c>
+      <c r="E567" t="n">
+        <v>324.1</v>
+      </c>
+      <c r="F567" t="n">
+        <v>327.33</v>
+      </c>
+      <c r="G567" t="n">
+        <v>329.49</v>
+      </c>
+      <c r="H567" t="n">
+        <v>346.12</v>
+      </c>
+      <c r="I567" t="n">
+        <v>338.47</v>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20726,7 +20870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B685"/>
+  <dimension ref="A1:B689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27579,6 +27723,46 @@
       </c>
       <c r="B685" t="n">
         <v>0.15</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-06-11 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-06-19 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>-0.66</v>
       </c>
     </row>
   </sheetData>
@@ -27747,28 +27931,28 @@
         <v>0.0593</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01922238322513157</v>
+        <v>0.02161854086006716</v>
       </c>
       <c r="J2" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="K2" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002938291907293999</v>
+        <v>0.0003777881649560388</v>
       </c>
       <c r="M2" t="n">
-        <v>6.880494411992411</v>
+        <v>6.844363113273487</v>
       </c>
       <c r="N2" t="n">
-        <v>67.81669063233062</v>
+        <v>67.36374670457904</v>
       </c>
       <c r="O2" t="n">
-        <v>8.235088987517416</v>
+        <v>8.207542062309461</v>
       </c>
       <c r="P2" t="n">
-        <v>316.1174926260277</v>
+        <v>316.0921329427915</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27825,28 +28009,28 @@
         <v>0.0791</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2280422688663302</v>
+        <v>0.2266704366824772</v>
       </c>
       <c r="J3" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="K3" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03235057655849005</v>
+        <v>0.03249681329271592</v>
       </c>
       <c r="M3" t="n">
-        <v>7.464293238400946</v>
+        <v>7.419123983177918</v>
       </c>
       <c r="N3" t="n">
-        <v>83.90955543385678</v>
+        <v>83.32730206532294</v>
       </c>
       <c r="O3" t="n">
-        <v>9.16021590541712</v>
+        <v>9.128378939621369</v>
       </c>
       <c r="P3" t="n">
-        <v>306.065278985795</v>
+        <v>306.0798121713619</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27903,28 +28087,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1234533367133787</v>
+        <v>0.1203395620865076</v>
       </c>
       <c r="J4" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="K4" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007993283563314857</v>
+        <v>0.007723593721566169</v>
       </c>
       <c r="M4" t="n">
-        <v>8.331940340207593</v>
+        <v>8.288613348811682</v>
       </c>
       <c r="N4" t="n">
-        <v>102.0327881553868</v>
+        <v>101.3481969998957</v>
       </c>
       <c r="O4" t="n">
-        <v>10.1011280635079</v>
+        <v>10.06718416439749</v>
       </c>
       <c r="P4" t="n">
-        <v>316.0835357437848</v>
+        <v>316.1165000820757</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27981,28 +28165,28 @@
         <v>0.0631</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09389591919709762</v>
+        <v>0.09364338436465375</v>
       </c>
       <c r="J5" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="K5" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00657317941941693</v>
+        <v>0.006647938967215494</v>
       </c>
       <c r="M5" t="n">
-        <v>7.076695242062038</v>
+        <v>7.032782705746448</v>
       </c>
       <c r="N5" t="n">
-        <v>71.87842070366885</v>
+        <v>71.37667368061807</v>
       </c>
       <c r="O5" t="n">
-        <v>8.478114218602439</v>
+        <v>8.448471677209913</v>
       </c>
       <c r="P5" t="n">
-        <v>322.4469922905753</v>
+        <v>322.4496655001569</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28059,28 +28243,28 @@
         <v>0.0548</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08914949730775797</v>
+        <v>0.08729931666182142</v>
       </c>
       <c r="J6" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="K6" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01090101538693289</v>
+        <v>0.0106290350201953</v>
       </c>
       <c r="M6" t="n">
-        <v>4.978986788815914</v>
+        <v>4.953985802636006</v>
       </c>
       <c r="N6" t="n">
-        <v>38.90051018387805</v>
+        <v>38.64318736824723</v>
       </c>
       <c r="O6" t="n">
-        <v>6.237027351541601</v>
+        <v>6.216364481612001</v>
       </c>
       <c r="P6" t="n">
-        <v>327.2118296397609</v>
+        <v>327.2314192971503</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28137,28 +28321,28 @@
         <v>0.1959</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1986608040374826</v>
+        <v>0.1971620648280633</v>
       </c>
       <c r="J7" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="K7" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09600875672543852</v>
+        <v>0.09611648866081912</v>
       </c>
       <c r="M7" t="n">
-        <v>3.543941536782417</v>
+        <v>3.526435845847135</v>
       </c>
       <c r="N7" t="n">
-        <v>20.04575656740815</v>
+        <v>19.91348228204844</v>
       </c>
       <c r="O7" t="n">
-        <v>4.477248772115321</v>
+        <v>4.46245249633522</v>
       </c>
       <c r="P7" t="n">
-        <v>324.4973111973408</v>
+        <v>324.5131730678401</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28215,28 +28399,28 @@
         <v>0.0625</v>
       </c>
       <c r="I8" t="n">
-        <v>0.006698833145474915</v>
+        <v>0.01613109373671425</v>
       </c>
       <c r="J8" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="K8" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001536130939308045</v>
+        <v>0.00088892417894193</v>
       </c>
       <c r="M8" t="n">
-        <v>2.848572288689504</v>
+        <v>2.872228517150086</v>
       </c>
       <c r="N8" t="n">
-        <v>15.75607584595193</v>
+        <v>15.93171809073267</v>
       </c>
       <c r="O8" t="n">
-        <v>3.969392377424021</v>
+        <v>3.991455635571147</v>
       </c>
       <c r="P8" t="n">
-        <v>339.7319877732988</v>
+        <v>339.6321217234748</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28293,28 +28477,28 @@
         <v>0.0762</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03459230714464305</v>
+        <v>0.031725580728322</v>
       </c>
       <c r="J9" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="K9" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002552828149300024</v>
+        <v>0.002180459545357061</v>
       </c>
       <c r="M9" t="n">
-        <v>3.863608786162824</v>
+        <v>3.851794759297135</v>
       </c>
       <c r="N9" t="n">
-        <v>25.22156763930496</v>
+        <v>25.09048527843704</v>
       </c>
       <c r="O9" t="n">
-        <v>5.022107888059053</v>
+        <v>5.009040355041776</v>
       </c>
       <c r="P9" t="n">
-        <v>341.1289770411464</v>
+        <v>341.1593420077115</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28352,7 +28536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J563"/>
+  <dimension ref="A1:J567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57631,6 +57815,214 @@
         </is>
       </c>
     </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>-36.96169977429221,175.8431683931755</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>-36.96241796629493,175.84325614130415</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>-36.963130483478196,175.84347422307928</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>-36.96383509379045,175.8437920748478</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>-36.964514177572305,175.84415650894275</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>-36.96517397184171,175.8445128384548</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>-36.965783347335964,175.84501237297073</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>-36.96645630382132,175.84533746454468</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-11 21:58:57+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>-36.96169977429221,175.8431683931755</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>-36.96241796629493,175.84325614130415</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>-36.963130483478196,175.84347422307928</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>-36.96383093482247,175.8438073850916</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>-36.964514177572305,175.84415650894275</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>-36.96517397184171,175.8445128384548</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>-36.965783347335964,175.84501237297073</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>-36.96646978216709,175.84530034032434</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:15+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>-36.96169959413493,175.84316949294308</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>-36.962420470488524,175.8432408543936</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>-36.96312603518061,175.84349678724914</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>-36.9638283354665,175.84381695399304</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>-36.96450754216884,175.8441761679684</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>-36.9651706662102,175.8445225525528</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>-36.96577898131867,175.84502518455628</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>-36.96646896529796,175.8453025902775</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>-36.96170409806384,175.84314199875217</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>-36.96242120913518,175.84323634530463</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>-36.96313013964859,175.84347596716984</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>-36.96383408293036,175.84379579608776</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>-36.96451662219384,175.84414926614295</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>-36.96516954088867,175.8445258594796</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>-36.96578292481822,175.84501361280164</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>-36.9664730867736,175.8452912382407</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
